--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:46:49+00:00</t>
+    <t>2026-03-23T16:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -734,7 +734,7 @@
     <t>Organization.identifier:cliaNum.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_cliaNum</t>
+    <t>http://openelis-global.org/org_cliaNum</t>
   </si>
   <si>
     <t>Organization.identifier:cliaNum.value</t>
@@ -767,7 +767,7 @@
     <t>Organization.identifier:shortName.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_shortName</t>
+    <t>http://openelis-global.org/org_shortName</t>
   </si>
   <si>
     <t>Organization.identifier:shortName.value</t>
@@ -800,7 +800,7 @@
     <t>Organization.identifier:code.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_code</t>
+    <t>http://openelis-global.org/org_code</t>
   </si>
   <si>
     <t>Organization.identifier:code.value</t>
@@ -833,7 +833,7 @@
     <t>Organization.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_uuid</t>
+    <t>http://openelis-global.org/org_uuid</t>
   </si>
   <si>
     <t>Organization.identifier:uuid.value</t>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:01:57+00:00</t>
+    <t>2026-05-11T11:00:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elisorganisation.xlsx
+++ b/StructureDefinition-open-elisorganisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:00:24+00:00</t>
+    <t>2026-05-11T11:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
